--- a/artfynd/A 30950-2026 artfynd.xlsx
+++ b/artfynd/A 30950-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136164356</v>
       </c>
       <c r="B4" t="n">
-        <v>92113</v>
+        <v>92116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>136164445</v>
       </c>
       <c r="B14" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>136164447</v>
       </c>
       <c r="B15" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136164446</v>
       </c>
       <c r="B20" t="n">
-        <v>100964</v>
+        <v>100967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>136164408</v>
       </c>
       <c r="B21" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>136164412</v>
       </c>
       <c r="B22" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>136164455</v>
       </c>
       <c r="B23" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>136164451</v>
       </c>
       <c r="B27" t="n">
-        <v>103917</v>
+        <v>103920</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>136164396</v>
       </c>
       <c r="B28" t="n">
-        <v>104865</v>
+        <v>104868</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>136164399</v>
       </c>
       <c r="B29" t="n">
-        <v>99619</v>
+        <v>99622</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>136164415</v>
       </c>
       <c r="B30" t="n">
-        <v>99619</v>
+        <v>99622</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136164450</v>
       </c>
       <c r="B31" t="n">
-        <v>99619</v>
+        <v>99622</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>136164583</v>
       </c>
       <c r="B32" t="n">
-        <v>99619</v>
+        <v>99622</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136164398</v>
       </c>
       <c r="B33" t="n">
-        <v>99148</v>
+        <v>99151</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>136164403</v>
       </c>
       <c r="B34" t="n">
-        <v>99148</v>
+        <v>99151</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>136164406</v>
       </c>
       <c r="B35" t="n">
-        <v>99148</v>
+        <v>99151</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>136164419</v>
       </c>
       <c r="B36" t="n">
-        <v>99148</v>
+        <v>99151</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30950-2026 artfynd.xlsx
+++ b/artfynd/A 30950-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136164356</v>
       </c>
       <c r="B4" t="n">
-        <v>92116</v>
+        <v>92117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>136164445</v>
       </c>
       <c r="B14" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>136164447</v>
       </c>
       <c r="B15" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136164446</v>
       </c>
       <c r="B20" t="n">
-        <v>100967</v>
+        <v>100968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>136164408</v>
       </c>
       <c r="B21" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>136164412</v>
       </c>
       <c r="B22" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>136164455</v>
       </c>
       <c r="B23" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>136164451</v>
       </c>
       <c r="B27" t="n">
-        <v>103920</v>
+        <v>103921</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>136164396</v>
       </c>
       <c r="B28" t="n">
-        <v>104868</v>
+        <v>104869</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>136164399</v>
       </c>
       <c r="B29" t="n">
-        <v>99622</v>
+        <v>99623</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>136164415</v>
       </c>
       <c r="B30" t="n">
-        <v>99622</v>
+        <v>99623</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136164450</v>
       </c>
       <c r="B31" t="n">
-        <v>99622</v>
+        <v>99623</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>136164583</v>
       </c>
       <c r="B32" t="n">
-        <v>99622</v>
+        <v>99623</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136164398</v>
       </c>
       <c r="B33" t="n">
-        <v>99151</v>
+        <v>99152</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>136164403</v>
       </c>
       <c r="B34" t="n">
-        <v>99151</v>
+        <v>99152</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>136164406</v>
       </c>
       <c r="B35" t="n">
-        <v>99151</v>
+        <v>99152</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>136164419</v>
       </c>
       <c r="B36" t="n">
-        <v>99151</v>
+        <v>99152</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30950-2026 artfynd.xlsx
+++ b/artfynd/A 30950-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136164356</v>
       </c>
       <c r="B4" t="n">
-        <v>92117</v>
+        <v>92122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>136164355</v>
       </c>
       <c r="B8" t="n">
-        <v>80011</v>
+        <v>80013</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>136164360</v>
       </c>
       <c r="B9" t="n">
-        <v>80011</v>
+        <v>80013</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136164366</v>
       </c>
       <c r="B10" t="n">
-        <v>80011</v>
+        <v>80013</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136164397</v>
       </c>
       <c r="B11" t="n">
-        <v>80011</v>
+        <v>80013</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>136164448</v>
       </c>
       <c r="B12" t="n">
-        <v>80011</v>
+        <v>80013</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>136164445</v>
       </c>
       <c r="B14" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>136164447</v>
       </c>
       <c r="B15" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136164446</v>
       </c>
       <c r="B20" t="n">
-        <v>100968</v>
+        <v>100973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>136164408</v>
       </c>
       <c r="B21" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>136164412</v>
       </c>
       <c r="B22" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>136164455</v>
       </c>
       <c r="B23" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>136164451</v>
       </c>
       <c r="B27" t="n">
-        <v>103921</v>
+        <v>103926</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>136164396</v>
       </c>
       <c r="B28" t="n">
-        <v>104869</v>
+        <v>104874</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>136164399</v>
       </c>
       <c r="B29" t="n">
-        <v>99623</v>
+        <v>99628</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>136164415</v>
       </c>
       <c r="B30" t="n">
-        <v>99623</v>
+        <v>99628</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136164450</v>
       </c>
       <c r="B31" t="n">
-        <v>99623</v>
+        <v>99628</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>136164583</v>
       </c>
       <c r="B32" t="n">
-        <v>99623</v>
+        <v>99628</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136164398</v>
       </c>
       <c r="B33" t="n">
-        <v>99152</v>
+        <v>99157</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>136164403</v>
       </c>
       <c r="B34" t="n">
-        <v>99152</v>
+        <v>99157</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>136164406</v>
       </c>
       <c r="B35" t="n">
-        <v>99152</v>
+        <v>99157</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>136164419</v>
       </c>
       <c r="B36" t="n">
-        <v>99152</v>
+        <v>99157</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
